--- a/規格計算.xlsx
+++ b/規格計算.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newxu\Desktop\newfolder\xuan_folder\梅子炊熟機\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newxu\Desktop\newfolder\xuan_folder\plum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F343A8D8-A22E-473E-A983-EC4BC1EE1BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD052236-1F75-4F1E-8AD2-F78E410621B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C962034F-368D-4A37-A150-BC03F9DD7AFF}"/>
   </bookViews>
   <sheets>
-    <sheet name="總計算" sheetId="1" r:id="rId1"/>
-    <sheet name="熱交換機" sheetId="2" r:id="rId2"/>
-    <sheet name="壓縮機" sheetId="3" r:id="rId3"/>
-    <sheet name="加熱器" sheetId="4" r:id="rId4"/>
-    <sheet name="風機" sheetId="5" r:id="rId5"/>
-    <sheet name="膨脹閥" sheetId="6" r:id="rId6"/>
-    <sheet name="蒸發器" sheetId="7" r:id="rId7"/>
-    <sheet name="冷凝器" sheetId="8" r:id="rId8"/>
+    <sheet name="純溫度計算" sheetId="1" r:id="rId1"/>
+    <sheet name="溫濕度計算" sheetId="9" r:id="rId2"/>
+    <sheet name="熱交換機" sheetId="2" r:id="rId3"/>
+    <sheet name="壓縮機" sheetId="3" r:id="rId4"/>
+    <sheet name="加熱器" sheetId="4" r:id="rId5"/>
+    <sheet name="風機" sheetId="5" r:id="rId6"/>
+    <sheet name="膨脹閥" sheetId="6" r:id="rId7"/>
+    <sheet name="蒸發器" sheetId="7" r:id="rId8"/>
+    <sheet name="冷凝器" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1491,6 +1492,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9ED92F1-9330-4DBB-A0A0-E67E8AFF2829}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9D0AC8-D085-47A7-848D-7BD3663CB9CF}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1882,7 +1893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A5A202-A533-4CDE-87B9-4CB1A89EDA06}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1953,7 +1964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCB9CE8-DE80-454B-AFBC-A0E5ED38DA6F}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -2139,7 +2150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78012F0F-EAE4-4FF2-891F-47E631DEF623}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -2426,7 +2437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DC14F3-55EC-4FC4-9319-E2BCBC513082}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -2559,7 +2570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE69C75-1C0F-4682-8652-6EAE5F167C04}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -2633,7 +2644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEC155B-31F4-4D6A-8A1B-8BE0B4A6A16E}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>

--- a/規格計算.xlsx
+++ b/規格計算.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newxu\Desktop\newfolder\xuan_folder\plum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD052236-1F75-4F1E-8AD2-F78E410621B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2698A8-2662-4DDF-A39A-14F0EB52FD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C962034F-368D-4A37-A150-BC03F9DD7AFF}"/>
   </bookViews>
@@ -502,22 +502,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>壓縮機輸入功 a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加熱器輸入功 b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>風機輸入功 c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>總輸入功 a+b+c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>COP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -545,14 +529,6 @@
   </si>
   <si>
     <t>空氣比熱 kJ/kg.K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>環境溫度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>環境濕度(未用)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -714,6 +690,30 @@
   </si>
   <si>
     <t>全熱機轉換效率 e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境溫度 °C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境相對濕度(未用)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>壓縮機輸入功 a (kW)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加熱器輸入功 b (kW)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風機輸入功 c (kW)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總輸入功 a+b+c (kW)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +771,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -784,8 +784,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -855,13 +861,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -907,6 +931,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -929,15 +974,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>899160</xdr:colOff>
+      <xdr:colOff>876300</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>130874</xdr:rowOff>
+      <xdr:rowOff>168974</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -966,7 +1011,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3025140" y="784860"/>
+          <a:off x="3002280" y="822960"/>
           <a:ext cx="5920740" cy="3582734"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1289,44 +1334,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="17">
         <v>30</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>161</v>
-      </c>
       <c r="M2" s="10"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3">
+      <c r="A3" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="18">
         <v>0</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -1337,11 +1382,11 @@
         <v>30</v>
       </c>
       <c r="F3" s="12">
-        <f>E3-(B19*B10/(1-B10))</f>
+        <f>E3-(B19*B9/(1-B9))</f>
         <v>16.277119889359501</v>
       </c>
       <c r="G3" s="12">
-        <f>B2-(B19/(1-B10))</f>
+        <f>B2-(B19/(1-B9))</f>
         <v>7.1285331489324975</v>
       </c>
       <c r="H3" s="12">
@@ -1349,15 +1394,15 @@
         <v>20.851413259573</v>
       </c>
       <c r="I3" s="12">
-        <f>(B2-B19)+((B20-B21)/(1-B10))-B20-B21</f>
+        <f>(B2-B19)+((B20-B21)/(1-B9))-B20-B21</f>
         <v>46.679056098193449</v>
       </c>
       <c r="J3" s="12">
-        <f>(B2-B19)+((B20-B21)/(1-B10))-B21</f>
+        <f>(B2-B19)+((B20-B21)/(1-B9))-B21</f>
         <v>63.89748465727375</v>
       </c>
-      <c r="K3" s="12">
-        <f>(B2-B19)+((B20-B21)/(1-B10))</f>
+      <c r="K3" s="21">
+        <f>(B2-B19)+((B20-B21)/(1-B9))</f>
         <v>63.89748465727375</v>
       </c>
       <c r="L3" s="12">
@@ -1366,117 +1411,125 @@
       </c>
       <c r="M3" s="13"/>
     </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+    </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="18">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="18">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B10" s="18">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B11" s="18">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>146</v>
       </c>
-      <c r="B7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B14">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>147</v>
       </c>
-      <c r="B8">
+      <c r="B15">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="19">
         <f>SUM(B5:B7)</f>
         <v>2.54</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B11">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B13">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16">
-        <v>1.006</v>
-      </c>
-    </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B18">
-        <f>B13/3600*B15*B16</f>
+        <f>B12/3600*B14*B15</f>
         <v>0.48204166666666665</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B19">
-        <f>B5*B11*B12/B18</f>
+        <f>B5*B10*B11/B18</f>
         <v>9.1485867404270014</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B20">
-        <f>B5*(B11+1)/B18</f>
+        <f>B5*(B10+1)/B18</f>
         <v>17.218428559080301</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B21">
         <f>B6/B18</f>

--- a/規格計算.xlsx
+++ b/規格計算.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\newxu\Desktop\newfolder\xuan_folder\plum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2698A8-2662-4DDF-A39A-14F0EB52FD99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCB0906-D325-454A-8BF7-7EF4A015B7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C962034F-368D-4A37-A150-BC03F9DD7AFF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C962034F-368D-4A37-A150-BC03F9DD7AFF}"/>
   </bookViews>
   <sheets>
     <sheet name="純溫度計算" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="蒸發器" sheetId="7" r:id="rId8"/>
     <sheet name="冷凝器" sheetId="8" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="187">
   <si>
     <t>型號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -697,10 +697,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>環境相對濕度(未用)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>壓縮機輸入功 a (kW)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -714,6 +710,319 @@
   </si>
   <si>
     <t>總輸入功 a+b+c (kW)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境相對濕度 RH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大氣壓力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>環境相對濕度 RH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ΔT</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>room</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【環境空氣含水量 W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>】</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>環境飽和水氣壓 P</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sat0</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>大氣壓力 P</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>atm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (kPa)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【冷排極限含水量 W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>】</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冷排動態汽化潛熱 h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fg2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冷排飽和水氣壓 P</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sat2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冷排實際出口濕度 W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>冷排飽和濕度 W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sat2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>環境絕對濕度 W</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (kg/kg)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空氣比熱 Cp (kJ/kg.K)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">空氣密度 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>ρ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (kg/m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溫度 °C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相對濕度 RH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>絕對溼度 kg/kg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>絕對溼度 g/kg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -721,7 +1030,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.0000000"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -765,6 +1078,29 @@
       <vertAlign val="subscript"/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -885,7 +1221,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -950,6 +1286,63 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -982,7 +1375,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>168974</xdr:rowOff>
+      <xdr:rowOff>214694</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1013,6 +1406,61 @@
         <a:xfrm>
           <a:off x="3002280" y="822960"/>
           <a:ext cx="5920740" cy="3582734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>182881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>535552</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>220981</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="圖片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2133239-796D-4F52-97FA-5ECB19CE58C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3276600" y="1508761"/>
+          <a:ext cx="7119232" cy="4160520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1321,8 +1769,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BCD0FD-6FAF-446C-A048-4DC4C50C1C52}">
-  <dimension ref="A2:M21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:L22"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="9.77734375" customWidth="1"/>
@@ -1333,7 +1781,7 @@
     <col min="14" max="14" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" s="8" t="s">
         <v>162</v>
       </c>
@@ -1362,14 +1810,13 @@
       <c r="K2" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="10"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="15" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B3" s="18">
         <v>0</v>
@@ -1382,68 +1829,67 @@
         <v>30</v>
       </c>
       <c r="F3" s="12">
-        <f>E3-(B19*B9/(1-B9))</f>
+        <f>E3-(B20*B9/(1-B9))</f>
         <v>16.277119889359501</v>
       </c>
       <c r="G3" s="12">
-        <f>B2-(B19/(1-B9))</f>
+        <f>B2-(B20/(1-B9))</f>
         <v>7.1285331489324975</v>
       </c>
       <c r="H3" s="12">
-        <f>B2-B19</f>
+        <f>B2-B20</f>
         <v>20.851413259573</v>
       </c>
       <c r="I3" s="12">
-        <f>(B2-B19)+((B20-B21)/(1-B9))-B20-B21</f>
+        <f>(B2-B20)+((B21-B22)/(1-B9))-B21-B22</f>
         <v>46.679056098193449</v>
       </c>
       <c r="J3" s="12">
-        <f>(B2-B19)+((B20-B21)/(1-B9))-B21</f>
+        <f>(B2-B20)+((B21-B22)/(1-B9))-B22</f>
         <v>63.89748465727375</v>
       </c>
       <c r="K3" s="21">
-        <f>(B2-B19)+((B20-B21)/(1-B9))</f>
+        <f>(B2-B20)+((B21-B22)/(1-B9))</f>
         <v>63.89748465727375</v>
       </c>
-      <c r="L3" s="12">
-        <f>B2-B19+B20+B21</f>
+      <c r="L3" s="13">
+        <f>B2-B20+B21+B22</f>
         <v>38.069841818653302</v>
       </c>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="15"/>
       <c r="B4" s="16"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="18">
         <v>0.54</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" s="15" t="s">
         <v>161</v>
       </c>
@@ -1451,7 +1897,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" s="15" t="s">
         <v>144</v>
       </c>
@@ -1459,7 +1905,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" s="15" t="s">
         <v>145</v>
       </c>
@@ -1467,7 +1913,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" s="11" t="s">
         <v>160</v>
       </c>
@@ -1475,7 +1921,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="18.600000000000001">
       <c r="A14" t="s">
         <v>146</v>
       </c>
@@ -1483,7 +1929,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>147</v>
       </c>
@@ -1491,73 +1937,660 @@
         <v>1.006</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="19">
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="19">
         <f>SUM(B5:B7)</f>
         <v>2.54</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>156</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <f>B12/3600*B14*B15</f>
         <v>0.48204166666666665</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:2" ht="19.8">
+      <c r="A20" t="s">
         <v>157</v>
       </c>
-      <c r="B19">
-        <f>B5*B10*B11/B18</f>
+      <c r="B20">
+        <f>B5*B10*B11/B19</f>
         <v>9.1485867404270014</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:2" ht="19.8">
+      <c r="A21" t="s">
         <v>158</v>
       </c>
-      <c r="B20">
-        <f>B5*(B10+1)/B18</f>
+      <c r="B21">
+        <f>B5*(B10+1)/B19</f>
         <v>17.218428559080301</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="19.8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:2" ht="19.8">
+      <c r="A22" t="s">
         <v>159</v>
       </c>
-      <c r="B21">
-        <f>B6/B18</f>
+      <c r="B22">
+        <f>B6/B19</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9ED92F1-9330-4DBB-A0A0-E67E8AFF2829}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A2:N34"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" customWidth="1"/>
+    <col min="9" max="10" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="9.77734375" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14">
+      <c r="A2" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="24">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="19.8">
+      <c r="A3" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="26">
+        <v>80</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="29">
+        <f>B2</f>
+        <v>30</v>
+      </c>
+      <c r="F3" s="30">
+        <f ca="1">E3 - (B22 * B10) / (1 - B10)</f>
+        <v>11.193971588861402</v>
+      </c>
+      <c r="G3" s="30">
+        <f ca="1">E3 - (B22 / (1 - B10))</f>
+        <v>-1.3433806852309971</v>
+      </c>
+      <c r="H3" s="30">
+        <f ca="1">E3 - B22</f>
+        <v>17.462647725907601</v>
+      </c>
+      <c r="I3" s="30">
+        <f ca="1">K3 - B24 - B23</f>
+        <v>32.295267287944355</v>
+      </c>
+      <c r="J3" s="30">
+        <f ca="1">K3 - B24</f>
+        <v>49.811442277915397</v>
+      </c>
+      <c r="K3" s="31">
+        <f ca="1">H3 + (B23 + B24 - B10 * B4) / (1 - B10)</f>
+        <v>46.253085200835194</v>
+      </c>
+      <c r="L3" s="31">
+        <f ca="1">K3 - B4</f>
+        <v>36.253085200835194</v>
+      </c>
+      <c r="M3" s="32">
+        <f ca="1">H3 + B23 + B24 - B4</f>
+        <v>24.978822715878636</v>
+      </c>
+      <c r="N3" s="33"/>
+    </row>
+    <row r="4" spans="1:14" ht="19.8">
+      <c r="A4" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="26">
+        <v>10</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="29">
+        <f>( (E6 *B17 / (E6 + 0.622)) / (0.61078 * EXP((17.27 * E3) / (E3 + 237.3))) ) * 100</f>
+        <v>80</v>
+      </c>
+      <c r="F4" s="30">
+        <f ca="1">( (F6 * B17 / (F6 + 0.622)) / (0.61078 * EXP((17.27 * F3) / (F3+ 237.3))) ) * 100</f>
+        <v>255.27263374748088</v>
+      </c>
+      <c r="G4" s="30">
+        <f ca="1">( (G6 * B17 / (G6 + 0.622)) / (0.61078 * EXP((17.27 * G3) / (G3 + 237.3))) ) * 100</f>
+        <v>613.15771053754258</v>
+      </c>
+      <c r="H4" s="30">
+        <f ca="1">( (H6 *B17 / (H6 + 0.622)) / (0.61078 * EXP((17.27 * H3) / (H3 + 237.3))) ) * 100</f>
+        <v>170.12441440253872</v>
+      </c>
+      <c r="I4" s="30">
+        <f ca="1">( (I6 * B17 / (I6 + 0.622)) / (0.61078 * EXP((17.27 * I3) / (I3 + 237.3))) ) * 100</f>
+        <v>70.210375482402981</v>
+      </c>
+      <c r="J4" s="30">
+        <f ca="1">( (J6 *B17 / (J6 + 0.622)) / (0.61078 * EXP((17.27 * J3) / (J3 + 237.3))) ) * 100</f>
+        <v>27.773912422418917</v>
+      </c>
+      <c r="K4" s="31">
+        <f ca="1">( (K6 *B17 / (K6 + 0.622)) / (0.61078 * EXP((17.27 * K3) / (K3+ 237.3))) ) * 100</f>
+        <v>33.222307675635513</v>
+      </c>
+      <c r="L4" s="31">
+        <f ca="1">( (L6 *B17 / (L6 + 0.622)) / (0.61078 * EXP((17.27 * L3) / (L3+ 237.3))) ) * 100</f>
+        <v>66.842014139105046</v>
+      </c>
+      <c r="M4" s="32">
+        <f ca="1">( (M6 * B17 / (M6 + 0.622)) / (0.61078 * EXP((17.27 * M3) / (M3 + 237.3))) ) * 100</f>
+        <v>127.27031796922405</v>
+      </c>
+      <c r="N4" s="33"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="25"/>
+      <c r="B5" s="28"/>
+      <c r="D5" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="36">
+        <f t="shared" ref="E5:M5" si="0">E6*1000</f>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="F5" s="36">
+        <f t="shared" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="G5" s="36">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="H5" s="36">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="I5" s="36">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="J5" s="36">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="K5" s="37">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.558928110257011</v>
+      </c>
+      <c r="L5" s="37">
+        <f t="shared" ca="1" si="0"/>
+        <v>25.739709472676015</v>
+      </c>
+      <c r="M5" s="38">
+        <f t="shared" ca="1" si="0"/>
+        <v>25.739709472676015</v>
+      </c>
+      <c r="N5" s="33"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="39">
+        <f>B28</f>
+        <v>2.155892811025701E-2</v>
+      </c>
+      <c r="F6" s="39">
+        <f>B28</f>
+        <v>2.155892811025701E-2</v>
+      </c>
+      <c r="G6" s="39">
+        <f ca="1">B34</f>
+        <v>2.1792199745801388E-3</v>
+      </c>
+      <c r="H6" s="39">
+        <f ca="1">B34</f>
+        <v>2.1792199745801388E-3</v>
+      </c>
+      <c r="I6" s="39">
+        <f ca="1">B34</f>
+        <v>2.1792199745801388E-3</v>
+      </c>
+      <c r="J6" s="39">
+        <f ca="1">B34</f>
+        <v>2.1792199745801388E-3</v>
+      </c>
+      <c r="K6" s="40">
+        <f ca="1">B34</f>
+        <v>2.1792199745801388E-3</v>
+      </c>
+      <c r="L6" s="40">
+        <f ca="1">B34 + (B16 * B4) / (2501 - 2.38 * L3)</f>
+        <v>6.3453385143242124E-3</v>
+      </c>
+      <c r="M6" s="39">
+        <f ca="1">B34 + (B16 * B4) / (2501 - 2.38 * L3)</f>
+        <v>6.3453385143242124E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="18">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="18">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="18">
+        <f ca="1">MAX(1.5, 3.15 - 0.015 * ((J3 - G3) - 30))</f>
+        <v>2.8326776555528039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="18">
+        <f ca="1">IFERROR((B16 * (F3 - G3)) / (B16 * (F3 - G3) + B31 * (B28 - B34)), 1)</f>
+        <v>0.20536060063468889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="18.600000000000001">
+      <c r="A15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="22">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="22">
+        <v>1.006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="19.8">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="19">
+        <v>101.325</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="19">
+        <f>SUM(B6:B8)</f>
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21">
+        <f>B13/3600*B15*B16</f>
+        <v>0.48204166666666665</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="19.8">
+      <c r="A22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22">
+        <f ca="1" xml:space="preserve"> (B6*B11 * B12) / B21</f>
+        <v>2.8962826658769196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="19.8">
+      <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23">
+        <f ca="1">( B6* (B11 + 1)) / B21</f>
+        <v>19.082222574106794</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="19.8">
+      <c r="A24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24">
+        <f xml:space="preserve"> B7 / B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="19.8">
+      <c r="A26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="19.8">
+      <c r="A27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27">
+        <f>0.61078 * EXP((17.27 *E3) / (E3 + 237.3))</f>
+        <v>4.2429261240812544</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="19.8">
+      <c r="A28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28">
+        <f>0.622 * (B27 * (B3/100)) / (B17 - B27 * (B3/100))</f>
+        <v>2.155892811025701E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="19.8">
+      <c r="A30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="19.8">
+      <c r="A31" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31">
+        <f ca="1">2501 - (2.38 * G3)</f>
+        <v>2504.1972460308498</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="19.8">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32">
+        <f ca="1">0.61078 * EXP((17.27 * G3) / (G3 + 237.3))</f>
+        <v>0.5535836606032819</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="19.8">
+      <c r="A33" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33">
+        <f ca="1">0.622 *B32 / (B17 - B32)</f>
+        <v>3.4169316002818297E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="19.8">
+      <c r="A34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34">
+        <f ca="1">IF(B28 &gt; B33, B33,B28)</f>
+        <v>3.4169316002818297E-3</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <cellWatches>
+    <cellWatch r="A2"/>
+    <cellWatch r="B2"/>
+    <cellWatch r="C2"/>
+    <cellWatch r="D2"/>
+    <cellWatch r="E2"/>
+    <cellWatch r="F2"/>
+    <cellWatch r="G2"/>
+    <cellWatch r="H2"/>
+    <cellWatch r="I2"/>
+    <cellWatch r="J2"/>
+    <cellWatch r="K2"/>
+    <cellWatch r="L2"/>
+    <cellWatch r="M2"/>
+    <cellWatch r="A3"/>
+    <cellWatch r="B3"/>
+    <cellWatch r="C3"/>
+    <cellWatch r="D3"/>
+    <cellWatch r="E3"/>
+    <cellWatch r="F3"/>
+    <cellWatch r="G3"/>
+    <cellWatch r="H3"/>
+    <cellWatch r="I3"/>
+    <cellWatch r="J3"/>
+    <cellWatch r="K3"/>
+    <cellWatch r="L3"/>
+    <cellWatch r="M3"/>
+    <cellWatch r="A4"/>
+    <cellWatch r="B4"/>
+    <cellWatch r="C4"/>
+    <cellWatch r="D4"/>
+    <cellWatch r="E4"/>
+    <cellWatch r="F4"/>
+    <cellWatch r="G4"/>
+    <cellWatch r="H4"/>
+    <cellWatch r="I4"/>
+    <cellWatch r="J4"/>
+    <cellWatch r="K4"/>
+    <cellWatch r="L4"/>
+    <cellWatch r="M4"/>
+    <cellWatch r="A5"/>
+    <cellWatch r="B5"/>
+    <cellWatch r="C5"/>
+    <cellWatch r="D5"/>
+    <cellWatch r="E5"/>
+    <cellWatch r="F5"/>
+    <cellWatch r="G5"/>
+    <cellWatch r="H5"/>
+    <cellWatch r="I5"/>
+    <cellWatch r="J5"/>
+    <cellWatch r="K5"/>
+    <cellWatch r="L5"/>
+    <cellWatch r="M5"/>
+    <cellWatch r="A6"/>
+    <cellWatch r="B6"/>
+    <cellWatch r="C6"/>
+    <cellWatch r="D6"/>
+    <cellWatch r="E6"/>
+    <cellWatch r="F6"/>
+    <cellWatch r="G6"/>
+    <cellWatch r="H6"/>
+    <cellWatch r="I6"/>
+    <cellWatch r="J6"/>
+    <cellWatch r="K6"/>
+    <cellWatch r="L6"/>
+    <cellWatch r="M6"/>
+    <cellWatch r="A7"/>
+    <cellWatch r="B7"/>
+    <cellWatch r="C7"/>
+    <cellWatch r="D7"/>
+    <cellWatch r="E7"/>
+    <cellWatch r="F7"/>
+    <cellWatch r="G7"/>
+    <cellWatch r="H7"/>
+    <cellWatch r="I7"/>
+    <cellWatch r="J7"/>
+    <cellWatch r="K7"/>
+    <cellWatch r="L7"/>
+    <cellWatch r="M7"/>
+    <cellWatch r="A8"/>
+    <cellWatch r="B8"/>
+    <cellWatch r="C8"/>
+    <cellWatch r="D8"/>
+    <cellWatch r="E8"/>
+    <cellWatch r="F8"/>
+    <cellWatch r="G8"/>
+    <cellWatch r="H8"/>
+    <cellWatch r="I8"/>
+    <cellWatch r="J8"/>
+    <cellWatch r="K8"/>
+    <cellWatch r="L8"/>
+    <cellWatch r="M8"/>
+    <cellWatch r="A9"/>
+    <cellWatch r="B9"/>
+    <cellWatch r="C9"/>
+    <cellWatch r="D9"/>
+    <cellWatch r="E9"/>
+    <cellWatch r="F9"/>
+    <cellWatch r="G9"/>
+    <cellWatch r="H9"/>
+    <cellWatch r="I9"/>
+    <cellWatch r="J9"/>
+    <cellWatch r="K9"/>
+    <cellWatch r="L9"/>
+    <cellWatch r="M9"/>
+    <cellWatch r="A10"/>
+    <cellWatch r="B10"/>
+    <cellWatch r="C10"/>
+    <cellWatch r="D10"/>
+    <cellWatch r="E10"/>
+    <cellWatch r="F10"/>
+    <cellWatch r="G10"/>
+    <cellWatch r="H10"/>
+    <cellWatch r="I10"/>
+    <cellWatch r="J10"/>
+    <cellWatch r="K10"/>
+    <cellWatch r="L10"/>
+    <cellWatch r="M10"/>
+    <cellWatch r="A11"/>
+    <cellWatch r="B11"/>
+    <cellWatch r="C11"/>
+    <cellWatch r="D11"/>
+    <cellWatch r="E11"/>
+    <cellWatch r="F11"/>
+    <cellWatch r="G11"/>
+    <cellWatch r="H11"/>
+    <cellWatch r="I11"/>
+    <cellWatch r="J11"/>
+    <cellWatch r="K11"/>
+    <cellWatch r="L11"/>
+    <cellWatch r="M11"/>
+    <cellWatch r="A12"/>
+    <cellWatch r="B12"/>
+    <cellWatch r="C12"/>
+    <cellWatch r="D12"/>
+    <cellWatch r="E12"/>
+    <cellWatch r="F12"/>
+    <cellWatch r="G12"/>
+    <cellWatch r="H12"/>
+    <cellWatch r="I12"/>
+    <cellWatch r="J12"/>
+    <cellWatch r="K12"/>
+    <cellWatch r="L12"/>
+    <cellWatch r="M12"/>
+    <cellWatch r="A13"/>
+    <cellWatch r="B13"/>
+    <cellWatch r="C13"/>
+    <cellWatch r="D13"/>
+    <cellWatch r="E13"/>
+    <cellWatch r="F13"/>
+    <cellWatch r="G13"/>
+    <cellWatch r="H13"/>
+    <cellWatch r="I13"/>
+    <cellWatch r="J13"/>
+    <cellWatch r="K13"/>
+    <cellWatch r="L13"/>
+    <cellWatch r="M13"/>
+  </cellWatches>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9D0AC8-D085-47A7-848D-7BD3663CB9CF}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" customWidth="1"/>
@@ -1567,12 +2600,12 @@
     <col min="7" max="11" width="8.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -1592,7 +2625,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>118</v>
       </c>
@@ -1612,7 +2645,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -1632,7 +2665,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -1652,7 +2685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -1672,7 +2705,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -1692,7 +2725,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -1712,7 +2745,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -1732,7 +2765,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -1752,7 +2785,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -1772,7 +2805,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>128</v>
       </c>
@@ -1792,7 +2825,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>129</v>
       </c>
@@ -1812,7 +2845,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -1832,7 +2865,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>131</v>
       </c>
@@ -1852,7 +2885,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -1872,7 +2905,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -1892,7 +2925,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -1912,7 +2945,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -1932,7 +2965,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="7"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1949,13 +2982,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A5A202-A533-4CDE-87B9-4CB1A89EDA06}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1963,7 +2996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1971,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1979,7 +3012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1987,7 +3020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1995,7 +3028,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2003,7 +3036,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2014,13 +3047,14 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCB9CE8-DE80-454B-AFBC-A0E5ED38DA6F}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.21875" bestFit="1" customWidth="1"/>
@@ -2028,7 +3062,7 @@
     <col min="4" max="5" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2045,7 +3079,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -2062,7 +3096,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -2079,7 +3113,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2096,7 +3130,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2113,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -2130,7 +3164,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>50</v>
       </c>
@@ -2147,7 +3181,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2164,7 +3198,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -2181,7 +3215,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>58</v>
       </c>
@@ -2189,7 +3223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -2206,7 +3240,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78012F0F-EAE4-4FF2-891F-47E631DEF623}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
@@ -2219,7 +3253,7 @@
     <col min="15" max="15" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +3279,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -2268,7 +3302,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2291,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2314,7 +3348,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2337,7 +3371,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2360,7 +3394,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="G7" t="s">
         <v>77</v>
       </c>
@@ -2380,10 +3414,10 @@
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="G9" t="s">
         <v>78</v>
       </c>
@@ -2403,7 +3437,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="G10" t="s">
         <v>80</v>
       </c>
@@ -2423,7 +3457,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="G11" t="s">
         <v>81</v>
       </c>
@@ -2443,7 +3477,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="G12" t="s">
         <v>82</v>
       </c>
@@ -2463,7 +3497,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="G13" s="4" t="s">
         <v>83</v>
       </c>
@@ -2493,18 +3527,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DC14F3-55EC-4FC4-9319-E2BCBC513082}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="87.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -2512,7 +3546,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -2520,7 +3554,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -2528,7 +3562,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -2536,7 +3570,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -2544,7 +3578,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -2552,7 +3586,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2560,7 +3594,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -2568,7 +3602,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -2576,7 +3610,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -2584,7 +3618,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>104</v>
       </c>
@@ -2592,7 +3626,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>106</v>
       </c>
@@ -2600,7 +3634,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>108</v>
       </c>
@@ -2608,7 +3642,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>110</v>
       </c>
@@ -2626,14 +3660,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE69C75-1C0F-4682-8652-6EAE5F167C04}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="30.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2641,7 +3675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2652,22 +3686,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2675,7 +3709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
         <v>142</v>
       </c>
@@ -2683,7 +3717,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2700,19 +3734,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EEC155B-31F4-4D6A-8A1B-8BE0B4A6A16E}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2723,22 +3757,22 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2746,7 +3780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>142</v>
       </c>
